--- a/data/trans_bre/IP16B03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 0,0</t>
+          <t>-67,54; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 0,0</t>
+          <t>-67,54; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,06</t>
+          <t>0,0; 34,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,46</t>
+          <t>0,0; 53,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Provincia-trans_bre.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 0,0</t>
+          <t>-66,74; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 0,0</t>
+          <t>-66,74; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,58</t>
+          <t>0,0; 37,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,26</t>
+          <t>0,0; 60,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
